--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.57526407071721</v>
+        <v>6.268480411491547</v>
       </c>
       <c r="D2" t="n">
-        <v>38.32715212814227</v>
+        <v>6.228162220823118</v>
       </c>
       <c r="E2" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F2" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.46323343453962</v>
+        <v>4.950275433112689</v>
       </c>
       <c r="D3" t="n">
-        <v>30.46589291287178</v>
+        <v>4.950707598341665</v>
       </c>
       <c r="E3" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F3" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.50516755462284</v>
+        <v>7.232089727626211</v>
       </c>
       <c r="D4" t="n">
-        <v>43.99800088941563</v>
+        <v>7.14967514453004</v>
       </c>
       <c r="E4" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F4" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.14186317853096</v>
+        <v>6.035552766511281</v>
       </c>
       <c r="D5" t="n">
-        <v>37.49908400789325</v>
+        <v>6.093601151282653</v>
       </c>
       <c r="E5" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F5" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.60181526678317</v>
+        <v>4.160294980852265</v>
       </c>
       <c r="D6" t="n">
-        <v>25.80562836198277</v>
+        <v>4.1934146088222</v>
       </c>
       <c r="E6" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F6" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.59862943482786</v>
+        <v>2.859777283159527</v>
       </c>
       <c r="D7" t="n">
-        <v>17.49023025267818</v>
+        <v>2.842162416060204</v>
       </c>
       <c r="E7" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F7" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.0426906569216</v>
+        <v>3.744437231749761</v>
       </c>
       <c r="D8" t="n">
-        <v>23.41257693630294</v>
+        <v>3.804543752149228</v>
       </c>
       <c r="E8" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F8" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.54120782406963</v>
+        <v>5.775446271411315</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94445880096674</v>
+        <v>5.840974555157096</v>
       </c>
       <c r="E9" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F9" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.78599583683497</v>
+        <v>3.215224323485684</v>
       </c>
       <c r="D10" t="n">
-        <v>19.38379811033331</v>
+        <v>3.149867192929163</v>
       </c>
       <c r="E10" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F10" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.10476479367938</v>
+        <v>5.704524278972899</v>
       </c>
       <c r="D11" t="n">
-        <v>35.50965614151858</v>
+        <v>5.77031912299677</v>
       </c>
       <c r="E11" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F11" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.08374021263402</v>
+        <v>3.588607784553028</v>
       </c>
       <c r="D12" t="n">
-        <v>22.45060599035379</v>
+        <v>3.648223473432492</v>
       </c>
       <c r="E12" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F12" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.9180659487922</v>
+        <v>5.674185716678732</v>
       </c>
       <c r="D13" t="n">
-        <v>35.30708153498443</v>
+        <v>5.737400749434971</v>
       </c>
       <c r="E13" t="n">
-        <v>8.180546709408866</v>
+        <v>1.329338840278941</v>
       </c>
       <c r="F13" t="n">
-        <v>8.165819313762938</v>
+        <v>1.326945638486477</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
